--- a/data/nzd0077/nzd0077.xlsx
+++ b/data/nzd0077/nzd0077.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K343"/>
+  <dimension ref="A1:K345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13821,6 +13821,84 @@
         <v>359.27</v>
       </c>
       <c r="K343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>319.51</v>
+      </c>
+      <c r="C344" t="n">
+        <v>330.13</v>
+      </c>
+      <c r="D344" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="E344" t="n">
+        <v>333.51</v>
+      </c>
+      <c r="F344" t="n">
+        <v>337.21</v>
+      </c>
+      <c r="G344" t="n">
+        <v>346.26</v>
+      </c>
+      <c r="H344" t="n">
+        <v>348.46</v>
+      </c>
+      <c r="I344" t="n">
+        <v>362.58</v>
+      </c>
+      <c r="J344" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>319.51</v>
+      </c>
+      <c r="C345" t="n">
+        <v>330.13</v>
+      </c>
+      <c r="D345" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="E345" t="n">
+        <v>332.17</v>
+      </c>
+      <c r="F345" t="n">
+        <v>336.85</v>
+      </c>
+      <c r="G345" t="n">
+        <v>347.2</v>
+      </c>
+      <c r="H345" t="n">
+        <v>347.56</v>
+      </c>
+      <c r="I345" t="n">
+        <v>361.93</v>
+      </c>
+      <c r="J345" t="n">
+        <v>359.94</v>
+      </c>
+      <c r="K345" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13837,7 +13915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17370,6 +17448,26 @@
       </c>
       <c r="B353" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -17538,28 +17636,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.162735471680726</v>
+        <v>0.1598248459921914</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06610064540669558</v>
+        <v>0.06456852369490429</v>
       </c>
       <c r="M2" t="n">
-        <v>3.492250471665018</v>
+        <v>3.486687849868151</v>
       </c>
       <c r="N2" t="n">
-        <v>20.35498564339913</v>
+        <v>20.27271079004951</v>
       </c>
       <c r="O2" t="n">
-        <v>4.511649991233709</v>
+        <v>4.502522713995956</v>
       </c>
       <c r="P2" t="n">
-        <v>317.7477250738392</v>
+        <v>317.7778900734394</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17616,28 +17714,28 @@
         <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1813615654426267</v>
+        <v>0.18030909601718</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1039346398839799</v>
+        <v>0.1040126639685993</v>
       </c>
       <c r="M3" t="n">
-        <v>3.04183570341451</v>
+        <v>3.029582264075139</v>
       </c>
       <c r="N3" t="n">
-        <v>15.42701336509584</v>
+        <v>15.34203738514311</v>
       </c>
       <c r="O3" t="n">
-        <v>3.927723687467823</v>
+        <v>3.916891290952956</v>
       </c>
       <c r="P3" t="n">
-        <v>326.2657315313106</v>
+        <v>326.2766390700974</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17694,28 +17792,28 @@
         <v>0.0862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1041282815531723</v>
+        <v>0.09993799843694536</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04148162477918449</v>
+        <v>0.03860506164704525</v>
       </c>
       <c r="M4" t="n">
-        <v>2.840281212073982</v>
+        <v>2.842226856860141</v>
       </c>
       <c r="N4" t="n">
-        <v>13.62994356328388</v>
+        <v>13.6254541964443</v>
       </c>
       <c r="O4" t="n">
-        <v>3.691875345035891</v>
+        <v>3.691267288675299</v>
       </c>
       <c r="P4" t="n">
-        <v>328.4831415152822</v>
+        <v>328.5265685573815</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17772,28 +17870,28 @@
         <v>0.0814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1381535754638274</v>
+        <v>0.1350284296059191</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08438765588922814</v>
+        <v>0.08157868655947309</v>
       </c>
       <c r="M5" t="n">
-        <v>2.345493098734912</v>
+        <v>2.348034457678662</v>
       </c>
       <c r="N5" t="n">
-        <v>11.26597919944629</v>
+        <v>11.24469788024228</v>
       </c>
       <c r="O5" t="n">
-        <v>3.356483159416458</v>
+        <v>3.353311479752855</v>
       </c>
       <c r="P5" t="n">
-        <v>331.905746833261</v>
+        <v>331.9381390025262</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17850,28 +17948,28 @@
         <v>0.0896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1465419560747871</v>
+        <v>0.145359777881609</v>
       </c>
       <c r="J6" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K6" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07365178724992072</v>
+        <v>0.0733905478122221</v>
       </c>
       <c r="M6" t="n">
-        <v>2.633462655281917</v>
+        <v>2.625090819649283</v>
       </c>
       <c r="N6" t="n">
-        <v>14.69355617222506</v>
+        <v>14.61427283213908</v>
       </c>
       <c r="O6" t="n">
-        <v>3.833217469988503</v>
+        <v>3.822861864119482</v>
       </c>
       <c r="P6" t="n">
-        <v>334.1990882433241</v>
+        <v>334.2113411124189</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17928,28 +18026,28 @@
         <v>0.1002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2518358817198058</v>
+        <v>0.2555545400445366</v>
       </c>
       <c r="J7" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K7" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2309537070940813</v>
+        <v>0.2375638682896969</v>
       </c>
       <c r="M7" t="n">
-        <v>2.529360220357629</v>
+        <v>2.529874669665598</v>
       </c>
       <c r="N7" t="n">
-        <v>11.48880171076055</v>
+        <v>11.48212830282962</v>
       </c>
       <c r="O7" t="n">
-        <v>3.389513491750778</v>
+        <v>3.388528929023569</v>
       </c>
       <c r="P7" t="n">
-        <v>336.8932218979105</v>
+        <v>336.8546799397168</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18006,28 +18104,28 @@
         <v>0.0829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2893095664998969</v>
+        <v>0.2915518508515618</v>
       </c>
       <c r="J8" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K8" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3064295931717763</v>
+        <v>0.3119873158334819</v>
       </c>
       <c r="M8" t="n">
-        <v>2.335106697142368</v>
+        <v>2.331166840992244</v>
       </c>
       <c r="N8" t="n">
-        <v>10.30617256547531</v>
+        <v>10.26888347408789</v>
       </c>
       <c r="O8" t="n">
-        <v>3.210322813281448</v>
+        <v>3.204509864876046</v>
       </c>
       <c r="P8" t="n">
-        <v>338.4644606173616</v>
+        <v>338.4412248164369</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18084,28 +18182,28 @@
         <v>0.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3388000231710326</v>
+        <v>0.3411069228629792</v>
       </c>
       <c r="J9" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K9" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3402570475853035</v>
+        <v>0.345760736392692</v>
       </c>
       <c r="M9" t="n">
-        <v>2.60899595951757</v>
+        <v>2.604802803575908</v>
       </c>
       <c r="N9" t="n">
-        <v>12.10783416690947</v>
+        <v>12.06074429951869</v>
       </c>
       <c r="O9" t="n">
-        <v>3.479631326291547</v>
+        <v>3.472858231992588</v>
       </c>
       <c r="P9" t="n">
-        <v>351.3515488052528</v>
+        <v>351.3276426155456</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18162,28 +18260,28 @@
         <v>0.1184</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2707073327263503</v>
+        <v>0.2753329867676805</v>
       </c>
       <c r="J10" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K10" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2779065829637141</v>
+        <v>0.2855677698804033</v>
       </c>
       <c r="M10" t="n">
-        <v>2.52073802670824</v>
+        <v>2.529867548612335</v>
       </c>
       <c r="N10" t="n">
-        <v>10.35873116131368</v>
+        <v>10.38963889714308</v>
       </c>
       <c r="O10" t="n">
-        <v>3.218498277351361</v>
+        <v>3.223296278213202</v>
       </c>
       <c r="P10" t="n">
-        <v>348.9031719846843</v>
+        <v>348.8552333203033</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18221,7 +18319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K343"/>
+  <dimension ref="A1:K345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37775,6 +37873,120 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-35.44713024420777,174.4272181728879</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-35.44787065824053,174.4268894047468</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-35.44865392625476,174.4267284118083</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-35.44940413335861,174.42674448376962</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-35.45014424469497,174.4267772738767</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-35.45088394933314,174.42688904313061</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-35.45161644002449,174.42702348156683</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-35.45232491110544,174.4272956605939</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-35.4530186318471,174.42758449071852</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-35.44713024420777,174.4272181728879</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-35.44787065824053,174.4268894047468</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-35.44865392625476,174.4267284118083</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-35.44940387571423,174.42672972432845</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-35.450144282476415,174.42677330798398</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-35.450883297581484,174.42689936863724</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-35.451617542448766,174.42701365794275</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-35.45232638280163,174.42728872882142</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-35.45301911648293,174.4275829478774</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0077/nzd0077.xlsx
+++ b/data/nzd0077/nzd0077.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K345"/>
+  <dimension ref="A1:K346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13901,6 +13901,45 @@
       <c r="K345" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>319.74</v>
+      </c>
+      <c r="C346" t="n">
+        <v>329.1</v>
+      </c>
+      <c r="D346" t="n">
+        <v>327.53</v>
+      </c>
+      <c r="E346" t="n">
+        <v>332.06</v>
+      </c>
+      <c r="F346" t="n">
+        <v>336.92</v>
+      </c>
+      <c r="G346" t="n">
+        <v>347.61</v>
+      </c>
+      <c r="H346" t="n">
+        <v>347.28</v>
+      </c>
+      <c r="I346" t="n">
+        <v>362.36</v>
+      </c>
+      <c r="J346" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17468,6 +17507,16 @@
       </c>
       <c r="B355" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -17636,28 +17685,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1598248459921914</v>
+        <v>0.1585243745153384</v>
       </c>
       <c r="J2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06456852369490429</v>
+        <v>0.06392554084736024</v>
       </c>
       <c r="M2" t="n">
-        <v>3.486687849868151</v>
+        <v>3.483110031219694</v>
       </c>
       <c r="N2" t="n">
-        <v>20.27271079004951</v>
+        <v>20.22850889754662</v>
       </c>
       <c r="O2" t="n">
-        <v>4.502522713995956</v>
+        <v>4.497611465827903</v>
       </c>
       <c r="P2" t="n">
-        <v>317.7778900734394</v>
+        <v>317.7914134036862</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17714,28 +17763,28 @@
         <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.18030909601718</v>
+        <v>0.1791911718953259</v>
       </c>
       <c r="J3" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1040126639685993</v>
+        <v>0.1033828132515021</v>
       </c>
       <c r="M3" t="n">
-        <v>3.029582264075139</v>
+        <v>3.026532100070578</v>
       </c>
       <c r="N3" t="n">
-        <v>15.34203738514311</v>
+        <v>15.30832671580946</v>
       </c>
       <c r="O3" t="n">
-        <v>3.916891290952956</v>
+        <v>3.912585681593371</v>
       </c>
       <c r="P3" t="n">
-        <v>326.2766390700974</v>
+        <v>326.2882641286702</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17792,28 +17841,28 @@
         <v>0.0862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09993799843694536</v>
+        <v>0.09783909275104229</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03860506164704525</v>
+        <v>0.03718785994409279</v>
       </c>
       <c r="M4" t="n">
-        <v>2.842226856860141</v>
+        <v>2.843221316621905</v>
       </c>
       <c r="N4" t="n">
-        <v>13.6254541964443</v>
+        <v>13.62388579725449</v>
       </c>
       <c r="O4" t="n">
-        <v>3.691267288675299</v>
+        <v>3.691054835308531</v>
       </c>
       <c r="P4" t="n">
-        <v>328.5265685573815</v>
+        <v>328.5483946375782</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17870,28 +17919,28 @@
         <v>0.0814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1350284296059191</v>
+        <v>0.1330442851902594</v>
       </c>
       <c r="J5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08157868655947309</v>
+        <v>0.07963270699719815</v>
       </c>
       <c r="M5" t="n">
-        <v>2.348034457678662</v>
+        <v>2.351434429880872</v>
       </c>
       <c r="N5" t="n">
-        <v>11.24469788024228</v>
+        <v>11.24599630214876</v>
       </c>
       <c r="O5" t="n">
-        <v>3.353311479752855</v>
+        <v>3.353505077101981</v>
       </c>
       <c r="P5" t="n">
-        <v>331.9381390025262</v>
+        <v>331.9587717043331</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17948,28 +17997,28 @@
         <v>0.0896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.145359777881609</v>
+        <v>0.1447091811249824</v>
       </c>
       <c r="J6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0733905478122221</v>
+        <v>0.07319652571745427</v>
       </c>
       <c r="M6" t="n">
-        <v>2.625090819649283</v>
+        <v>2.621264988772995</v>
       </c>
       <c r="N6" t="n">
-        <v>14.61427283213908</v>
+        <v>14.575556560989</v>
       </c>
       <c r="O6" t="n">
-        <v>3.822861864119482</v>
+        <v>3.817794724836446</v>
       </c>
       <c r="P6" t="n">
-        <v>334.2113411124189</v>
+        <v>334.218106531695</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18026,28 +18075,28 @@
         <v>0.1002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2555545400445366</v>
+        <v>0.2578720147488894</v>
       </c>
       <c r="J7" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K7" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2375638682896969</v>
+        <v>0.2412767683071705</v>
       </c>
       <c r="M7" t="n">
-        <v>2.529874669665598</v>
+        <v>2.532522232067994</v>
       </c>
       <c r="N7" t="n">
-        <v>11.48212830282962</v>
+        <v>11.49508247069605</v>
       </c>
       <c r="O7" t="n">
-        <v>3.388528929023569</v>
+        <v>3.390439863896135</v>
       </c>
       <c r="P7" t="n">
-        <v>336.8546799397168</v>
+        <v>336.8305810061197</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18104,28 +18153,28 @@
         <v>0.0829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2915518508515618</v>
+        <v>0.2922177854694141</v>
       </c>
       <c r="J8" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K8" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3119873158334819</v>
+        <v>0.3142575100820125</v>
       </c>
       <c r="M8" t="n">
-        <v>2.331166840992244</v>
+        <v>2.327321072860883</v>
       </c>
       <c r="N8" t="n">
-        <v>10.26888347408789</v>
+        <v>10.24293637190017</v>
       </c>
       <c r="O8" t="n">
-        <v>3.204509864876046</v>
+        <v>3.200458775222729</v>
       </c>
       <c r="P8" t="n">
-        <v>338.4412248164369</v>
+        <v>338.4342999019576</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18182,28 +18231,28 @@
         <v>0.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3411069228629792</v>
+        <v>0.3422834515432634</v>
       </c>
       <c r="J9" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K9" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.345760736392692</v>
+        <v>0.3485395437098836</v>
       </c>
       <c r="M9" t="n">
-        <v>2.604802803575908</v>
+        <v>2.602829352823811</v>
       </c>
       <c r="N9" t="n">
-        <v>12.06074429951869</v>
+        <v>12.03770222312464</v>
       </c>
       <c r="O9" t="n">
-        <v>3.472858231992588</v>
+        <v>3.469539194637329</v>
       </c>
       <c r="P9" t="n">
-        <v>351.3276426155456</v>
+        <v>351.315408140456</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18260,28 +18309,28 @@
         <v>0.1184</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2753329867676805</v>
+        <v>0.277722214811797</v>
       </c>
       <c r="J10" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K10" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2855677698804033</v>
+        <v>0.2894419496287253</v>
       </c>
       <c r="M10" t="n">
-        <v>2.529867548612335</v>
+        <v>2.534792667845975</v>
       </c>
       <c r="N10" t="n">
-        <v>10.38963889714308</v>
+        <v>10.40866711121019</v>
       </c>
       <c r="O10" t="n">
-        <v>3.223296278213202</v>
+        <v>3.226246598016059</v>
       </c>
       <c r="P10" t="n">
-        <v>348.8552333203033</v>
+        <v>348.8303882387689</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18319,7 +18368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K345"/>
+  <dimension ref="A1:K346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37987,6 +38036,63 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-35.447131170103205,174.42722044006132</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-35.44786798182523,174.4268785390397</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-35.44865387419856,174.4267276432529</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-35.449403854564245,174.42672851273258</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-35.45014427513003,174.42677407912979</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-35.450883013306544,174.4269038723156</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-35.451617885425065,174.42701060170407</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-35.45232540921804,174.42729331445557</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-35.45301811490221,174.42758613641567</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0077/nzd0077.xlsx
+++ b/data/nzd0077/nzd0077.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K346"/>
+  <dimension ref="A1:K347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13940,6 +13940,45 @@
       <c r="K346" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>322.23</v>
+      </c>
+      <c r="C347" t="n">
+        <v>326.49</v>
+      </c>
+      <c r="D347" t="n">
+        <v>326.97</v>
+      </c>
+      <c r="E347" t="n">
+        <v>332.61</v>
+      </c>
+      <c r="F347" t="n">
+        <v>336.92</v>
+      </c>
+      <c r="G347" t="n">
+        <v>350.6</v>
+      </c>
+      <c r="H347" t="n">
+        <v>348.62</v>
+      </c>
+      <c r="I347" t="n">
+        <v>362.03</v>
+      </c>
+      <c r="J347" t="n">
+        <v>360.54</v>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17517,6 +17556,16 @@
       </c>
       <c r="B356" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -17685,28 +17734,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1585243745153384</v>
+        <v>0.1586594430089893</v>
       </c>
       <c r="J2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06392554084736024</v>
+        <v>0.06441868705240639</v>
       </c>
       <c r="M2" t="n">
-        <v>3.483110031219694</v>
+        <v>3.473707373387058</v>
       </c>
       <c r="N2" t="n">
-        <v>20.22850889754662</v>
+        <v>20.17019896257818</v>
       </c>
       <c r="O2" t="n">
-        <v>4.497611465827903</v>
+        <v>4.4911244652735</v>
       </c>
       <c r="P2" t="n">
-        <v>317.7914134036862</v>
+        <v>317.7899968716798</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17763,28 +17812,28 @@
         <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1791911718953259</v>
+        <v>0.176535732572164</v>
       </c>
       <c r="J3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1033828132515021</v>
+        <v>0.1008854124571661</v>
       </c>
       <c r="M3" t="n">
-        <v>3.026532100070578</v>
+        <v>3.031243647182003</v>
       </c>
       <c r="N3" t="n">
-        <v>15.30832671580946</v>
+        <v>15.32359199674803</v>
       </c>
       <c r="O3" t="n">
-        <v>3.912585681593371</v>
+        <v>3.91453598741256</v>
       </c>
       <c r="P3" t="n">
-        <v>326.2882641286702</v>
+        <v>326.3161130717556</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17841,28 +17890,28 @@
         <v>0.0862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09783909275104229</v>
+        <v>0.09540473841574741</v>
       </c>
       <c r="J4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03718785994409279</v>
+        <v>0.03552227815736209</v>
       </c>
       <c r="M4" t="n">
-        <v>2.843221316621905</v>
+        <v>2.845537838890324</v>
       </c>
       <c r="N4" t="n">
-        <v>13.62388579725449</v>
+        <v>13.63452277894508</v>
       </c>
       <c r="O4" t="n">
-        <v>3.691054835308531</v>
+        <v>3.692495467694589</v>
       </c>
       <c r="P4" t="n">
-        <v>328.5483946375782</v>
+        <v>328.5739249499231</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17919,28 +17968,28 @@
         <v>0.0814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1330442851902594</v>
+        <v>0.1313622717916698</v>
       </c>
       <c r="J5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07963270699719815</v>
+        <v>0.07810299589656799</v>
       </c>
       <c r="M5" t="n">
-        <v>2.351434429880872</v>
+        <v>2.353199900547835</v>
       </c>
       <c r="N5" t="n">
-        <v>11.24599630214876</v>
+        <v>11.23736981948474</v>
       </c>
       <c r="O5" t="n">
-        <v>3.353505077101981</v>
+        <v>3.352218641360486</v>
       </c>
       <c r="P5" t="n">
-        <v>331.9587717043331</v>
+        <v>331.976411834536</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17997,28 +18046,28 @@
         <v>0.0896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1447091811249824</v>
+        <v>0.1440444079538401</v>
       </c>
       <c r="J6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K6" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07319652571745427</v>
+        <v>0.07299669117618679</v>
       </c>
       <c r="M6" t="n">
-        <v>2.621264988772995</v>
+        <v>2.617478354125874</v>
       </c>
       <c r="N6" t="n">
-        <v>14.575556560989</v>
+        <v>14.5371602285829</v>
       </c>
       <c r="O6" t="n">
-        <v>3.817794724836446</v>
+        <v>3.81276280780524</v>
       </c>
       <c r="P6" t="n">
-        <v>334.218106531695</v>
+        <v>334.2250783461312</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18075,28 +18124,28 @@
         <v>0.1002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2578720147488894</v>
+        <v>0.2619040904493377</v>
       </c>
       <c r="J7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K7" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2412767683071705</v>
+        <v>0.2460027866434714</v>
       </c>
       <c r="M7" t="n">
-        <v>2.532522232067994</v>
+        <v>2.54264505495163</v>
       </c>
       <c r="N7" t="n">
-        <v>11.49508247069605</v>
+        <v>11.59906383677661</v>
       </c>
       <c r="O7" t="n">
-        <v>3.390439863896135</v>
+        <v>3.405739836918934</v>
       </c>
       <c r="P7" t="n">
-        <v>336.8305810061197</v>
+        <v>336.7882945770085</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18153,28 +18202,28 @@
         <v>0.0829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2922177854694141</v>
+        <v>0.2936255991211482</v>
       </c>
       <c r="J8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3142575100820125</v>
+        <v>0.3173888873898001</v>
       </c>
       <c r="M8" t="n">
-        <v>2.327321072860883</v>
+        <v>2.32668939086218</v>
       </c>
       <c r="N8" t="n">
-        <v>10.24293637190017</v>
+        <v>10.23005882298954</v>
       </c>
       <c r="O8" t="n">
-        <v>3.200458775222729</v>
+        <v>3.19844631391392</v>
       </c>
       <c r="P8" t="n">
-        <v>338.4342999019576</v>
+        <v>338.4195354439939</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18231,28 +18280,28 @@
         <v>0.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3422834515432634</v>
+        <v>0.3432294209558472</v>
       </c>
       <c r="J9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3485395437098836</v>
+        <v>0.3511340283495715</v>
       </c>
       <c r="M9" t="n">
-        <v>2.602829352823811</v>
+        <v>2.599720603734117</v>
       </c>
       <c r="N9" t="n">
-        <v>12.03770222312464</v>
+        <v>12.0104632126296</v>
       </c>
       <c r="O9" t="n">
-        <v>3.469539194637329</v>
+        <v>3.46561152073189</v>
       </c>
       <c r="P9" t="n">
-        <v>351.315408140456</v>
+        <v>351.3054872779826</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18309,28 +18358,28 @@
         <v>0.1184</v>
       </c>
       <c r="I10" t="n">
-        <v>0.277722214811797</v>
+        <v>0.2802468102531275</v>
       </c>
       <c r="J10" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K10" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2894419496287253</v>
+        <v>0.2934574896165039</v>
       </c>
       <c r="M10" t="n">
-        <v>2.534792667845975</v>
+        <v>2.54037359851494</v>
       </c>
       <c r="N10" t="n">
-        <v>10.40866711121019</v>
+        <v>10.43237325869034</v>
       </c>
       <c r="O10" t="n">
-        <v>3.226246598016059</v>
+        <v>3.229918460068356</v>
       </c>
       <c r="P10" t="n">
-        <v>348.8303882387689</v>
+        <v>348.8039115220366</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18368,7 +18417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K346"/>
+  <dimension ref="A1:K347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38093,6 +38142,63 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-35.447141193925,174.42724498468095</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-35.44786119983636,174.42685100555198</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-35.44865345774892,174.42672149480944</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-35.44940396031408,174.4267345707121</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-35.45014427513003,174.42677407912979</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-35.450880940174514,174.4269367162128</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-35.45161624403785,174.42702522798888</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-35.45232615638686,174.427289795248</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-35.453017177939536,174.42758911924173</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0077/nzd0077.xlsx
+++ b/data/nzd0077/nzd0077.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K347"/>
+  <dimension ref="A1:K349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13979,6 +13979,84 @@
       <c r="K347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>321.99</v>
+      </c>
+      <c r="C348" t="n">
+        <v>325.11</v>
+      </c>
+      <c r="D348" t="n">
+        <v>326.27</v>
+      </c>
+      <c r="E348" t="n">
+        <v>330.41</v>
+      </c>
+      <c r="F348" t="n">
+        <v>335.96</v>
+      </c>
+      <c r="G348" t="n">
+        <v>350.78</v>
+      </c>
+      <c r="H348" t="n">
+        <v>347.08</v>
+      </c>
+      <c r="I348" t="n">
+        <v>360.74</v>
+      </c>
+      <c r="J348" t="n">
+        <v>360.97</v>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>316.21</v>
+      </c>
+      <c r="C349" t="n">
+        <v>323.14</v>
+      </c>
+      <c r="D349" t="n">
+        <v>325.1</v>
+      </c>
+      <c r="E349" t="n">
+        <v>330.41</v>
+      </c>
+      <c r="F349" t="n">
+        <v>335.04</v>
+      </c>
+      <c r="G349" t="n">
+        <v>350.77</v>
+      </c>
+      <c r="H349" t="n">
+        <v>345.19</v>
+      </c>
+      <c r="I349" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="J349" t="n">
+        <v>360.98</v>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13993,7 +14071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17566,6 +17644,26 @@
       </c>
       <c r="B357" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -17734,28 +17832,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1586594430089893</v>
+        <v>0.1552652622242712</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06441868705240639</v>
+        <v>0.06234588763433513</v>
       </c>
       <c r="M2" t="n">
-        <v>3.473707373387058</v>
+        <v>3.470485349299071</v>
       </c>
       <c r="N2" t="n">
-        <v>20.17019896257818</v>
+        <v>20.15061360992106</v>
       </c>
       <c r="O2" t="n">
-        <v>4.4911244652735</v>
+        <v>4.488943484821463</v>
       </c>
       <c r="P2" t="n">
-        <v>317.7899968716798</v>
+        <v>317.8258225398465</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17812,28 +17910,28 @@
         <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.176535732572164</v>
+        <v>0.1685386222995455</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1008854124571661</v>
+        <v>0.09238303350734178</v>
       </c>
       <c r="M3" t="n">
-        <v>3.031243647182003</v>
+        <v>3.054262889611413</v>
       </c>
       <c r="N3" t="n">
-        <v>15.32359199674803</v>
+        <v>15.51008182776694</v>
       </c>
       <c r="O3" t="n">
-        <v>3.91453598741256</v>
+        <v>3.938284122275453</v>
       </c>
       <c r="P3" t="n">
-        <v>326.3161130717556</v>
+        <v>326.4004900472617</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17890,28 +17988,28 @@
         <v>0.0862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09540473841574741</v>
+        <v>0.08911025363161812</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03552227815736209</v>
+        <v>0.03115369957267111</v>
       </c>
       <c r="M4" t="n">
-        <v>2.845537838890324</v>
+        <v>2.856290103307363</v>
       </c>
       <c r="N4" t="n">
-        <v>13.63452277894508</v>
+        <v>13.72478153638752</v>
       </c>
       <c r="O4" t="n">
-        <v>3.692495467694589</v>
+        <v>3.70469722600748</v>
       </c>
       <c r="P4" t="n">
-        <v>328.5739249499231</v>
+        <v>328.640336566253</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17968,28 +18066,28 @@
         <v>0.0814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1313622717916698</v>
+        <v>0.1254855129633297</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K5" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07810299589656799</v>
+        <v>0.07177480183382756</v>
       </c>
       <c r="M5" t="n">
-        <v>2.353199900547835</v>
+        <v>2.370723857498525</v>
       </c>
       <c r="N5" t="n">
-        <v>11.23736981948474</v>
+        <v>11.31809553469669</v>
       </c>
       <c r="O5" t="n">
-        <v>3.352218641360486</v>
+        <v>3.364237734568811</v>
       </c>
       <c r="P5" t="n">
-        <v>331.976411834536</v>
+        <v>332.0384130667097</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18046,28 +18144,28 @@
         <v>0.0896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1440444079538401</v>
+        <v>0.1410645063810207</v>
       </c>
       <c r="J6" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K6" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07299669117618679</v>
+        <v>0.07090333827425632</v>
       </c>
       <c r="M6" t="n">
-        <v>2.617478354125874</v>
+        <v>2.619207459897659</v>
       </c>
       <c r="N6" t="n">
-        <v>14.5371602285829</v>
+        <v>14.49220759587826</v>
       </c>
       <c r="O6" t="n">
-        <v>3.81276280780524</v>
+        <v>3.806863222638589</v>
       </c>
       <c r="P6" t="n">
-        <v>334.2250783461312</v>
+        <v>334.2565196475112</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18124,28 +18222,28 @@
         <v>0.1002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2619040904493377</v>
+        <v>0.2699932684565172</v>
       </c>
       <c r="J7" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K7" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2460027866434714</v>
+        <v>0.255464372208987</v>
       </c>
       <c r="M7" t="n">
-        <v>2.54264505495163</v>
+        <v>2.563480399796477</v>
       </c>
       <c r="N7" t="n">
-        <v>11.59906383677661</v>
+        <v>11.80771438644775</v>
       </c>
       <c r="O7" t="n">
-        <v>3.405739836918934</v>
+        <v>3.436235496360479</v>
       </c>
       <c r="P7" t="n">
-        <v>336.7882945770085</v>
+        <v>336.7029518296813</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18202,28 +18300,28 @@
         <v>0.0829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2936255991211482</v>
+        <v>0.2934729574030331</v>
       </c>
       <c r="J8" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K8" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3173888873898001</v>
+        <v>0.319899573161649</v>
       </c>
       <c r="M8" t="n">
-        <v>2.32668939086218</v>
+        <v>2.318865896369527</v>
       </c>
       <c r="N8" t="n">
-        <v>10.23005882298954</v>
+        <v>10.17654569393994</v>
       </c>
       <c r="O8" t="n">
-        <v>3.19844631391392</v>
+        <v>3.190069857219421</v>
       </c>
       <c r="P8" t="n">
-        <v>338.4195354439939</v>
+        <v>338.4211511898794</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18280,28 +18378,28 @@
         <v>0.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3432294209558472</v>
+        <v>0.3433087173826178</v>
       </c>
       <c r="J9" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K9" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3511340283495715</v>
+        <v>0.3542303070424456</v>
       </c>
       <c r="M9" t="n">
-        <v>2.599720603734117</v>
+        <v>2.585939129858766</v>
       </c>
       <c r="N9" t="n">
-        <v>12.0104632126296</v>
+        <v>11.94170748999315</v>
       </c>
       <c r="O9" t="n">
-        <v>3.46561152073189</v>
+        <v>3.455677573210954</v>
       </c>
       <c r="P9" t="n">
-        <v>351.3054872779826</v>
+        <v>351.3046518381441</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18358,28 +18456,28 @@
         <v>0.1184</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2802468102531275</v>
+        <v>0.2856715485847541</v>
       </c>
       <c r="J10" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K10" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2934574896165039</v>
+        <v>0.3017349874859108</v>
       </c>
       <c r="M10" t="n">
-        <v>2.54037359851494</v>
+        <v>2.553468902063139</v>
       </c>
       <c r="N10" t="n">
-        <v>10.43237325869034</v>
+        <v>10.49623175687867</v>
       </c>
       <c r="O10" t="n">
-        <v>3.229918460068356</v>
+        <v>3.239788844489509</v>
       </c>
       <c r="P10" t="n">
-        <v>348.8039115220366</v>
+        <v>348.7466792081137</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18417,7 +18515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K347"/>
+  <dimension ref="A1:K349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38199,6 +38297,120 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-35.44714022777373,174.42724261893423</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-35.44785761395461,174.42683644761775</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-35.4486529371864,174.42671380925526</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-35.449403537312904,174.42671033879387</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-35.45014437587996,174.42676350341586</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-35.4508808153703,174.4269386934373</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-35.451618130408065,174.42700841867645</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-35.45232907713672,174.42727603834496</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-35.4530157886499,174.42759354205265</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-35.44711695961611,174.4271856438838</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-35.44785249497537,174.42681566564127</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-35.44865206710226,174.42670096340058</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-35.449403537312904,174.42671033879387</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-35.450144472431106,174.42675336835669</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-35.45088082230387,174.4269385835915</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-35.45162044549563,174.42698778906458</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-35.452329982795284,174.42727177263836</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-35.45301575634084,174.4275936449087</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0077/nzd0077.xlsx
+++ b/data/nzd0077/nzd0077.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K349"/>
+  <dimension ref="A1:K351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14055,6 +14055,84 @@
         <v>360.98</v>
       </c>
       <c r="K349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>314.3</v>
+      </c>
+      <c r="C350" t="n">
+        <v>324.55</v>
+      </c>
+      <c r="D350" t="n">
+        <v>325.41</v>
+      </c>
+      <c r="E350" t="n">
+        <v>330.19</v>
+      </c>
+      <c r="F350" t="n">
+        <v>335.66</v>
+      </c>
+      <c r="G350" t="n">
+        <v>348.77</v>
+      </c>
+      <c r="H350" t="n">
+        <v>344.96</v>
+      </c>
+      <c r="I350" t="n">
+        <v>362.71</v>
+      </c>
+      <c r="J350" t="n">
+        <v>362.63</v>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>316.4</v>
+      </c>
+      <c r="C351" t="n">
+        <v>327.12</v>
+      </c>
+      <c r="D351" t="n">
+        <v>327.14</v>
+      </c>
+      <c r="E351" t="n">
+        <v>335.29</v>
+      </c>
+      <c r="F351" t="n">
+        <v>338.43</v>
+      </c>
+      <c r="G351" t="n">
+        <v>348.44</v>
+      </c>
+      <c r="H351" t="n">
+        <v>349.4</v>
+      </c>
+      <c r="I351" t="n">
+        <v>366.88</v>
+      </c>
+      <c r="J351" t="n">
+        <v>365.78</v>
+      </c>
+      <c r="K351" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14071,7 +14149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17664,6 +17742,26 @@
       </c>
       <c r="B359" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -17832,28 +17930,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1552652622242712</v>
+        <v>0.1476668294093153</v>
       </c>
       <c r="J2" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06234588763433513</v>
+        <v>0.05675458828664259</v>
       </c>
       <c r="M2" t="n">
-        <v>3.470485349299071</v>
+        <v>3.488423199677075</v>
       </c>
       <c r="N2" t="n">
-        <v>20.15061360992106</v>
+        <v>20.28869256692867</v>
       </c>
       <c r="O2" t="n">
-        <v>4.488943484821463</v>
+        <v>4.504297122407521</v>
       </c>
       <c r="P2" t="n">
-        <v>317.8258225398465</v>
+        <v>317.9062748800213</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17910,28 +18008,28 @@
         <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1685386222995455</v>
+        <v>0.1627224699106184</v>
       </c>
       <c r="J3" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K3" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09238303350734178</v>
+        <v>0.08690243918817975</v>
       </c>
       <c r="M3" t="n">
-        <v>3.054262889611413</v>
+        <v>3.066165369384415</v>
       </c>
       <c r="N3" t="n">
-        <v>15.51008182776694</v>
+        <v>15.57559724999521</v>
       </c>
       <c r="O3" t="n">
-        <v>3.938284122275453</v>
+        <v>3.946593119387304</v>
       </c>
       <c r="P3" t="n">
-        <v>326.4004900472617</v>
+        <v>326.4620688747435</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17988,28 +18086,28 @@
         <v>0.0862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08911025363161812</v>
+        <v>0.08366925800054245</v>
       </c>
       <c r="J4" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K4" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03115369957267111</v>
+        <v>0.02765999576822631</v>
       </c>
       <c r="M4" t="n">
-        <v>2.856290103307363</v>
+        <v>2.863751379467585</v>
       </c>
       <c r="N4" t="n">
-        <v>13.72478153638752</v>
+        <v>13.77724295618158</v>
       </c>
       <c r="O4" t="n">
-        <v>3.70469722600748</v>
+        <v>3.711770865258465</v>
       </c>
       <c r="P4" t="n">
-        <v>328.640336566253</v>
+        <v>328.6979452924119</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18066,28 +18164,28 @@
         <v>0.0814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1254855129633297</v>
+        <v>0.1224427988433716</v>
       </c>
       <c r="J5" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K5" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07177480183382756</v>
+        <v>0.0689694945670748</v>
       </c>
       <c r="M5" t="n">
-        <v>2.370723857498525</v>
+        <v>2.373535744802092</v>
       </c>
       <c r="N5" t="n">
-        <v>11.31809553469669</v>
+        <v>11.33020588259501</v>
       </c>
       <c r="O5" t="n">
-        <v>3.364237734568811</v>
+        <v>3.366037118422049</v>
       </c>
       <c r="P5" t="n">
-        <v>332.0384130667097</v>
+        <v>332.0706174947779</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18144,28 +18242,28 @@
         <v>0.0896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1410645063810207</v>
+        <v>0.1399341292519782</v>
       </c>
       <c r="J6" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K6" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07090333827425632</v>
+        <v>0.07062560641358151</v>
       </c>
       <c r="M6" t="n">
-        <v>2.619207459897659</v>
+        <v>2.613089273435669</v>
       </c>
       <c r="N6" t="n">
-        <v>14.49220759587826</v>
+        <v>14.42581137953661</v>
       </c>
       <c r="O6" t="n">
-        <v>3.806863222638589</v>
+        <v>3.798132617423542</v>
       </c>
       <c r="P6" t="n">
-        <v>334.2565196475112</v>
+        <v>334.2684812505711</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18222,28 +18320,28 @@
         <v>0.1002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2699932684565172</v>
+        <v>0.2753372317443112</v>
       </c>
       <c r="J7" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K7" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L7" t="n">
-        <v>0.255464372208987</v>
+        <v>0.2635038354754498</v>
       </c>
       <c r="M7" t="n">
-        <v>2.563480399796477</v>
+        <v>2.572503561540063</v>
       </c>
       <c r="N7" t="n">
-        <v>11.80771438644775</v>
+        <v>11.86254489631827</v>
       </c>
       <c r="O7" t="n">
-        <v>3.436235496360479</v>
+        <v>3.44420453752652</v>
       </c>
       <c r="P7" t="n">
-        <v>336.7029518296813</v>
+        <v>336.6463667006482</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18300,28 +18398,28 @@
         <v>0.0829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2934729574030331</v>
+        <v>0.2944981540669306</v>
       </c>
       <c r="J8" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K8" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L8" t="n">
-        <v>0.319899573161649</v>
+        <v>0.323560765258454</v>
       </c>
       <c r="M8" t="n">
-        <v>2.318865896369527</v>
+        <v>2.317659541438992</v>
       </c>
       <c r="N8" t="n">
-        <v>10.17654569393994</v>
+        <v>10.15085272604955</v>
       </c>
       <c r="O8" t="n">
-        <v>3.190069857219421</v>
+        <v>3.18604028945799</v>
       </c>
       <c r="P8" t="n">
-        <v>338.4211511898794</v>
+        <v>338.4102832595075</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18378,28 +18476,28 @@
         <v>0.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3433087173826178</v>
+        <v>0.3482241444349787</v>
       </c>
       <c r="J9" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K9" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3542303070424456</v>
+        <v>0.3612880117750558</v>
       </c>
       <c r="M9" t="n">
-        <v>2.585939129858766</v>
+        <v>2.594296588653475</v>
       </c>
       <c r="N9" t="n">
-        <v>11.94170748999315</v>
+        <v>12.00144982897427</v>
       </c>
       <c r="O9" t="n">
-        <v>3.455677573210954</v>
+        <v>3.464310873604485</v>
       </c>
       <c r="P9" t="n">
-        <v>351.3046518381441</v>
+        <v>351.2525918320072</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18456,28 +18554,28 @@
         <v>0.1184</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2856715485847541</v>
+        <v>0.2946145368636229</v>
       </c>
       <c r="J10" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K10" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3017349874859108</v>
+        <v>0.3104669349038756</v>
       </c>
       <c r="M10" t="n">
-        <v>2.553468902063139</v>
+        <v>2.584391260629148</v>
       </c>
       <c r="N10" t="n">
-        <v>10.49623175687867</v>
+        <v>10.79226308964774</v>
       </c>
       <c r="O10" t="n">
-        <v>3.239788844489509</v>
+        <v>3.285158000712864</v>
       </c>
       <c r="P10" t="n">
-        <v>348.7466792081137</v>
+        <v>348.6519750656092</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18515,7 +18613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K349"/>
+  <dimension ref="A1:K351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38411,6 +38509,120 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-35.44710927065135,174.42716681649532</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-35.447856158813664,174.4268305400506</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-35.448652297637516,174.42670436700308</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-35.44940349501253,174.42670791560204</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-35.45014440736412,174.42676019850526</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-35.45088220901559,174.42691661442979</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-35.45162072722562,174.42698527858263</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-35.45232461676614,174.42729704694838</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-35.45301042534428,174.42761061615843</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-35.44711772448678,174.42718751676557</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-35.44786283686874,174.42685765156585</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-35.44865358417117,174.42672336130119</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-35.449404475599856,174.42676408959449</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-35.45014411665692,174.42679071384634</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-35.450882437822635,174.42691298951803</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-35.4516152886027,174.42703374179612</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-35.452315175259166,174.4273415169283</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-35.45300024798071,174.42764301581053</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
